--- a/lamiaceae-nlr-conserved-core/results/conserved_core/tables/Table_S_per_species_NLR_summary.xlsx
+++ b/lamiaceae-nlr-conserved-core/results/conserved_core/tables/Table_S_per_species_NLR_summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="140">
   <si>
     <t>Species</t>
   </si>
@@ -83,6 +83,27 @@
     <t>tblastn_SAG101_bitscore</t>
   </si>
   <si>
+    <t>copies_Clade18_RNL_TNL</t>
+  </si>
+  <si>
+    <t>copies_Clade76</t>
+  </si>
+  <si>
+    <t>copies_Clade42</t>
+  </si>
+  <si>
+    <t>copies_Clade38</t>
+  </si>
+  <si>
+    <t>ZAR1_best_pident</t>
+  </si>
+  <si>
+    <t>ZAR1_best_bitscore</t>
+  </si>
+  <si>
+    <t>ZAR1_best_aln_len</t>
+  </si>
+  <si>
     <t>Agastache foeniculum</t>
   </si>
   <si>
@@ -380,6 +401,12 @@
     <t>tblastn_*</t>
   </si>
   <si>
+    <t>copies_Clade18_RNL_TNL, copies_Clade76, copies_Clade42, copies_Clade38</t>
+  </si>
+  <si>
+    <t>ZAR1_best_pident, ZAR1_best_bitscore, ZAR1_best_aln_len</t>
+  </si>
+  <si>
     <t>NB-ARC-containing proteins identified in the proteome.</t>
   </si>
   <si>
@@ -402,6 +429,12 @@
   </si>
   <si>
     <t>Best tblastn hit of the reference protein (EDS1 Solanum pennellii, PAD4 Olea europaea, SAG101 Olea europaea) against the genome: percent identity and bitscore.</t>
+  </si>
+  <si>
+    <t>Genes of each conserved NB-ARC clade per genome (cd-hit 85% clusters expanded to genes). Clade 18 contains the ADR1 and NRG1 helpers and also the TIR-NLR-like proteins of Callicarpa nudiflora and Elsholtzia splendens, so its count can exceed ADR1 + NRG1.</t>
+  </si>
+  <si>
+    <t>Best tblastn hit (highest bitscore) of the ZAR1 reference against the genome (E-value 1e-20): percent identity, bitscore and alignment length in amino acids. Identities of 28-32% are below the 57.7% observed between ZAR1 of N. benthamiana and A. thaliana, so no ZAR1 ortholog was detected.</t>
   </si>
 </sst>
 </file>
@@ -733,10 +766,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V47"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -803,13 +836,34 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C2">
         <v>312</v>
@@ -871,13 +925,34 @@
       <c r="V2">
         <v>89.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>29.162</v>
+      </c>
+      <c r="AB2">
+        <v>278</v>
+      </c>
+      <c r="AC2">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>324</v>
@@ -939,13 +1014,34 @@
       <c r="V3">
         <v>87.40000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>29.162</v>
+      </c>
+      <c r="AB3">
+        <v>278</v>
+      </c>
+      <c r="AC3">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C4">
         <v>392</v>
@@ -1007,13 +1103,34 @@
       <c r="V4">
         <v>157</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>29.492</v>
+      </c>
+      <c r="AB4">
+        <v>283</v>
+      </c>
+      <c r="AC4">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>467</v>
@@ -1075,13 +1192,34 @@
       <c r="V5">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>30.846</v>
+      </c>
+      <c r="AB5">
+        <v>298</v>
+      </c>
+      <c r="AC5">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>526</v>
@@ -1143,13 +1281,34 @@
       <c r="V6">
         <v>87</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>7</v>
+      </c>
+      <c r="Z6">
+        <v>4</v>
+      </c>
+      <c r="AA6">
+        <v>29.426</v>
+      </c>
+      <c r="AB6">
+        <v>272</v>
+      </c>
+      <c r="AC6">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>416</v>
@@ -1211,13 +1370,34 @@
       <c r="V7">
         <v>387</v>
       </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7">
+        <v>5</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>13</v>
+      </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>30.451</v>
+      </c>
+      <c r="AB7">
+        <v>296</v>
+      </c>
+      <c r="AC7">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C8">
         <v>311</v>
@@ -1279,13 +1459,34 @@
       <c r="V8">
         <v>153</v>
       </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>2</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>31.318</v>
+      </c>
+      <c r="AB8">
+        <v>301</v>
+      </c>
+      <c r="AC8">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>368</v>
@@ -1347,13 +1548,34 @@
       <c r="V9">
         <v>146</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>30.318</v>
+      </c>
+      <c r="AB9">
+        <v>286</v>
+      </c>
+      <c r="AC9">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10">
         <v>420</v>
@@ -1415,13 +1637,34 @@
       <c r="V10">
         <v>154</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>29.567</v>
+      </c>
+      <c r="AB10">
+        <v>280</v>
+      </c>
+      <c r="AC10">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>308</v>
@@ -1483,13 +1726,34 @@
       <c r="V11">
         <v>111</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>2</v>
+      </c>
+      <c r="AA11">
+        <v>29.262</v>
+      </c>
+      <c r="AB11">
+        <v>290</v>
+      </c>
+      <c r="AC11">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C12">
         <v>330</v>
@@ -1551,13 +1815,34 @@
       <c r="V12">
         <v>174</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="W12">
+        <v>2</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>2</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>30.938</v>
+      </c>
+      <c r="AB12">
+        <v>302</v>
+      </c>
+      <c r="AC12">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C13">
         <v>602</v>
@@ -1619,13 +1904,34 @@
       <c r="V13">
         <v>89</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="W13">
+        <v>2</v>
+      </c>
+      <c r="X13">
+        <v>2</v>
+      </c>
+      <c r="Y13">
+        <v>2</v>
+      </c>
+      <c r="Z13">
+        <v>7</v>
+      </c>
+      <c r="AA13">
+        <v>31.047</v>
+      </c>
+      <c r="AB13">
+        <v>301</v>
+      </c>
+      <c r="AC13">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C14">
         <v>942</v>
@@ -1687,13 +1993,34 @@
       <c r="V14">
         <v>159</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="W14">
+        <v>2</v>
+      </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
+        <v>3</v>
+      </c>
+      <c r="Z14">
+        <v>2</v>
+      </c>
+      <c r="AA14">
+        <v>29.54</v>
+      </c>
+      <c r="AB14">
+        <v>281</v>
+      </c>
+      <c r="AC14">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C15">
         <v>638</v>
@@ -1755,13 +2082,34 @@
       <c r="V15">
         <v>132</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>29.842</v>
+      </c>
+      <c r="AB15">
+        <v>292</v>
+      </c>
+      <c r="AC15">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C16">
         <v>668</v>
@@ -1823,13 +2171,34 @@
       <c r="V16">
         <v>90.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>2</v>
+      </c>
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16">
+        <v>31.103</v>
+      </c>
+      <c r="AB16">
+        <v>309</v>
+      </c>
+      <c r="AC16">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C17">
         <v>472</v>
@@ -1891,13 +2260,34 @@
       <c r="V17">
         <v>87</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>30.683</v>
+      </c>
+      <c r="AB17">
+        <v>301</v>
+      </c>
+      <c r="AC17">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C18">
         <v>389</v>
@@ -1959,13 +2349,34 @@
       <c r="V18">
         <v>92</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="W18">
+        <v>2</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>30.014</v>
+      </c>
+      <c r="AB18">
+        <v>236</v>
+      </c>
+      <c r="AC18">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C19">
         <v>962</v>
@@ -2027,13 +2438,34 @@
       <c r="V19">
         <v>93.59999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
+        <v>2</v>
+      </c>
+      <c r="Y19">
+        <v>3</v>
+      </c>
+      <c r="Z19">
+        <v>3</v>
+      </c>
+      <c r="AA19">
+        <v>30.562</v>
+      </c>
+      <c r="AB19">
+        <v>302</v>
+      </c>
+      <c r="AC19">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C20">
         <v>238</v>
@@ -2095,13 +2527,34 @@
       <c r="V20">
         <v>89.7</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>29.831</v>
+      </c>
+      <c r="AB20">
+        <v>289</v>
+      </c>
+      <c r="AC20">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>351</v>
@@ -2163,13 +2616,34 @@
       <c r="V21">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>3</v>
+      </c>
+      <c r="AA21">
+        <v>29.938</v>
+      </c>
+      <c r="AB21">
+        <v>292</v>
+      </c>
+      <c r="AC21">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C22">
         <v>1223</v>
@@ -2231,13 +2705,34 @@
       <c r="V22">
         <v>88.2</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="W22">
+        <v>4</v>
+      </c>
+      <c r="X22">
+        <v>2</v>
+      </c>
+      <c r="Y22">
+        <v>6</v>
+      </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
+      <c r="AA22">
+        <v>30.393</v>
+      </c>
+      <c r="AB22">
+        <v>295</v>
+      </c>
+      <c r="AC22">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C23">
         <v>601</v>
@@ -2299,13 +2794,34 @@
       <c r="V23">
         <v>87</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>2</v>
+      </c>
+      <c r="Z23">
+        <v>2</v>
+      </c>
+      <c r="AA23">
+        <v>31.585</v>
+      </c>
+      <c r="AB23">
+        <v>307</v>
+      </c>
+      <c r="AC23">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C24">
         <v>858</v>
@@ -2367,13 +2883,34 @@
       <c r="V24">
         <v>86.7</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>6</v>
+      </c>
+      <c r="Z24">
+        <v>2</v>
+      </c>
+      <c r="AA24">
+        <v>30.31</v>
+      </c>
+      <c r="AB24">
+        <v>281</v>
+      </c>
+      <c r="AC24">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C25">
         <v>2407</v>
@@ -2435,13 +2972,34 @@
       <c r="V25">
         <v>88.2</v>
       </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="W25">
+        <v>6</v>
+      </c>
+      <c r="X25">
+        <v>4</v>
+      </c>
+      <c r="Y25">
+        <v>13</v>
+      </c>
+      <c r="Z25">
+        <v>7</v>
+      </c>
+      <c r="AA25">
+        <v>30.944</v>
+      </c>
+      <c r="AB25">
+        <v>293</v>
+      </c>
+      <c r="AC25">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C26">
         <v>1036</v>
@@ -2503,13 +3061,34 @@
       <c r="V26">
         <v>94.40000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="W26">
+        <v>2</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>3</v>
+      </c>
+      <c r="AA26">
+        <v>30.446</v>
+      </c>
+      <c r="AB26">
+        <v>294</v>
+      </c>
+      <c r="AC26">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>172</v>
@@ -2571,13 +3150,34 @@
       <c r="V27">
         <v>73.2</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>28.444</v>
+      </c>
+      <c r="AB27">
+        <v>241</v>
+      </c>
+      <c r="AC27">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C28">
         <v>488</v>
@@ -2639,13 +3239,34 @@
       <c r="V28">
         <v>84</v>
       </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>10</v>
+      </c>
+      <c r="Z28">
+        <v>3</v>
+      </c>
+      <c r="AA28">
+        <v>30.21</v>
+      </c>
+      <c r="AB28">
+        <v>286</v>
+      </c>
+      <c r="AC28">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C29">
         <v>782</v>
@@ -2707,13 +3328,34 @@
       <c r="V29">
         <v>102</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="W29">
+        <v>2</v>
+      </c>
+      <c r="X29">
+        <v>2</v>
+      </c>
+      <c r="Y29">
+        <v>2</v>
+      </c>
+      <c r="Z29">
+        <v>4</v>
+      </c>
+      <c r="AA29">
+        <v>31.073</v>
+      </c>
+      <c r="AB29">
+        <v>293</v>
+      </c>
+      <c r="AC29">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C30">
         <v>901</v>
@@ -2775,13 +3417,34 @@
       <c r="V30">
         <v>156</v>
       </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="W30">
+        <v>4</v>
+      </c>
+      <c r="X30">
+        <v>3</v>
+      </c>
+      <c r="Y30">
+        <v>3</v>
+      </c>
+      <c r="Z30">
+        <v>6</v>
+      </c>
+      <c r="AA30">
+        <v>30.359</v>
+      </c>
+      <c r="AB30">
+        <v>299</v>
+      </c>
+      <c r="AC30">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C31">
         <v>396</v>
@@ -2843,13 +3506,34 @@
       <c r="V31">
         <v>151</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>1</v>
+      </c>
+      <c r="AA31">
+        <v>30.663</v>
+      </c>
+      <c r="AB31">
+        <v>248</v>
+      </c>
+      <c r="AC31">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C32">
         <v>438</v>
@@ -2911,13 +3595,34 @@
       <c r="V32">
         <v>149</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>1</v>
+      </c>
+      <c r="Y32">
+        <v>1</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>30.269</v>
+      </c>
+      <c r="AB32">
+        <v>244</v>
+      </c>
+      <c r="AC32">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C33">
         <v>685</v>
@@ -2979,13 +3684,34 @@
       <c r="V33">
         <v>114</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="W33">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
+        <v>1</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>30.725</v>
+      </c>
+      <c r="AB33">
+        <v>256</v>
+      </c>
+      <c r="AC33">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C34">
         <v>809</v>
@@ -3047,13 +3773,34 @@
       <c r="V34">
         <v>91.7</v>
       </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="W34">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>28.401</v>
+      </c>
+      <c r="AB34">
+        <v>256</v>
+      </c>
+      <c r="AC34">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C35">
         <v>309</v>
@@ -3115,13 +3862,34 @@
       <c r="V35">
         <v>91.7</v>
       </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="W35">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>1</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>1</v>
+      </c>
+      <c r="AA35">
+        <v>28.327</v>
+      </c>
+      <c r="AB35">
+        <v>262</v>
+      </c>
+      <c r="AC35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C36">
         <v>573</v>
@@ -3183,13 +3951,34 @@
       <c r="V36">
         <v>121</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="W36">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="Y36">
+        <v>2</v>
+      </c>
+      <c r="Z36">
+        <v>1</v>
+      </c>
+      <c r="AA36">
+        <v>28.224</v>
+      </c>
+      <c r="AB36">
+        <v>257</v>
+      </c>
+      <c r="AC36">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C37">
         <v>433</v>
@@ -3251,13 +4040,34 @@
       <c r="V37">
         <v>96.7</v>
       </c>
-    </row>
-    <row r="38" spans="1:22">
+      <c r="W37">
+        <v>2</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37">
+        <v>2</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>30.813</v>
+      </c>
+      <c r="AB37">
+        <v>254</v>
+      </c>
+      <c r="AC37">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C38">
         <v>539</v>
@@ -3319,13 +4129,34 @@
       <c r="V38">
         <v>153</v>
       </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="W38">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="Y38">
+        <v>1</v>
+      </c>
+      <c r="Z38">
+        <v>1</v>
+      </c>
+      <c r="AA38">
+        <v>29.759</v>
+      </c>
+      <c r="AB38">
+        <v>282</v>
+      </c>
+      <c r="AC38">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C39">
         <v>545</v>
@@ -3387,13 +4218,34 @@
       <c r="V39">
         <v>114</v>
       </c>
-    </row>
-    <row r="40" spans="1:22">
+      <c r="W39">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="Y39">
+        <v>2</v>
+      </c>
+      <c r="Z39">
+        <v>2</v>
+      </c>
+      <c r="AA39">
+        <v>28.502</v>
+      </c>
+      <c r="AB39">
+        <v>271</v>
+      </c>
+      <c r="AC39">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C40">
         <v>443</v>
@@ -3455,13 +4307,34 @@
       <c r="V40">
         <v>122</v>
       </c>
-    </row>
-    <row r="41" spans="1:22">
+      <c r="W40">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
+        <v>1</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>29.926</v>
+      </c>
+      <c r="AB40">
+        <v>293</v>
+      </c>
+      <c r="AC40">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C41">
         <v>436</v>
@@ -3523,13 +4396,34 @@
       <c r="V41">
         <v>160</v>
       </c>
-    </row>
-    <row r="42" spans="1:22">
+      <c r="W41">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>2</v>
+      </c>
+      <c r="Z41">
+        <v>2</v>
+      </c>
+      <c r="AA41">
+        <v>30.417</v>
+      </c>
+      <c r="AB41">
+        <v>279</v>
+      </c>
+      <c r="AC41">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C42">
         <v>424</v>
@@ -3591,13 +4485,34 @@
       <c r="V42">
         <v>160</v>
       </c>
-    </row>
-    <row r="43" spans="1:22">
+      <c r="W42">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
+        <v>2</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>29.476</v>
+      </c>
+      <c r="AB42">
+        <v>281</v>
+      </c>
+      <c r="AC42">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C43">
         <v>499</v>
@@ -3659,13 +4574,34 @@
       <c r="V43">
         <v>79.7</v>
       </c>
-    </row>
-    <row r="44" spans="1:22">
+      <c r="W43">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
+        <v>2</v>
+      </c>
+      <c r="Z43">
+        <v>3</v>
+      </c>
+      <c r="AA43">
+        <v>27.64</v>
+      </c>
+      <c r="AB43">
+        <v>288</v>
+      </c>
+      <c r="AC43">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C44">
         <v>207</v>
@@ -3727,13 +4663,34 @@
       <c r="V44">
         <v>87.40000000000001</v>
       </c>
-    </row>
-    <row r="45" spans="1:22">
+      <c r="W44">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>2</v>
+      </c>
+      <c r="Z44">
+        <v>1</v>
+      </c>
+      <c r="AA44">
+        <v>29.842</v>
+      </c>
+      <c r="AB44">
+        <v>280</v>
+      </c>
+      <c r="AC44">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C45">
         <v>595</v>
@@ -3795,13 +4752,34 @@
       <c r="V45">
         <v>89</v>
       </c>
-    </row>
-    <row r="46" spans="1:22">
+      <c r="W45">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>1</v>
+      </c>
+      <c r="Y45">
+        <v>1</v>
+      </c>
+      <c r="Z45">
+        <v>1</v>
+      </c>
+      <c r="AA45">
+        <v>30.073</v>
+      </c>
+      <c r="AB45">
+        <v>280</v>
+      </c>
+      <c r="AC45">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C46">
         <v>1039</v>
@@ -3863,13 +4841,34 @@
       <c r="V46">
         <v>147</v>
       </c>
-    </row>
-    <row r="47" spans="1:22">
+      <c r="W46">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="Y46">
+        <v>2</v>
+      </c>
+      <c r="Z46">
+        <v>4</v>
+      </c>
+      <c r="AA46">
+        <v>30</v>
+      </c>
+      <c r="AB46">
+        <v>285</v>
+      </c>
+      <c r="AC46">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C47">
         <v>938</v>
@@ -3930,6 +4929,27 @@
       </c>
       <c r="V47">
         <v>147</v>
+      </c>
+      <c r="W47">
+        <v>1</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="Y47">
+        <v>2</v>
+      </c>
+      <c r="Z47">
+        <v>2</v>
+      </c>
+      <c r="AA47">
+        <v>30.024</v>
+      </c>
+      <c r="AB47">
+        <v>285</v>
+      </c>
+      <c r="AC47">
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -3939,15 +4959,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3955,23 +4975,23 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3979,23 +4999,23 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4003,15 +5023,31 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
